--- a/s04/descargables/S04_ALU_04_Checklist_Beneficiario_Controlador.xlsx
+++ b/s04/descargables/S04_ALU_04_Checklist_Beneficiario_Controlador.xlsx
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="234" uniqueCount="202">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="236" uniqueCount="204">
   <si>
     <t xml:space="preserve">Checklist de Beneficiario Controlador</t>
   </si>
@@ -99,6 +99,12 @@
     <t xml:space="preserve">El último párrafo del RCG 23 Quinquies no pide el nombre: pide el procedimiento. Hay que documentar cómo se llegó a esa persona, conservar lo que lo sustenta, mantenerlo actualizado durante la Relación de negocios y resguardarlo por los diez años del L 18 fr. IV. Por eso este archivo tiene una hoja de cadena de control y no sólo una casilla.</t>
   </si>
   <si>
+    <t xml:space="preserve">Y hay una tercera obligación, en otro ordenamiento</t>
+  </si>
+  <si>
+    <t xml:space="preserve">El artículo 32-B Ter del Código Fiscal de la Federación obliga a personas morales, fideicomisos y partes contratantes a obtener y conservar la información de su beneficiario controlador ante el SAT, con umbral de MÁS DEL 15 %, no de 25 %. La constancia rendida ante una autoridad no libera ante la otra: es insumo, no sustituto. Y un beneficiario determinado con el umbral fiscal no se traslada a este régimen sin revisarlo.</t>
+  </si>
+  <si>
     <t xml:space="preserve">Las fechas</t>
   </si>
   <si>
@@ -189,7 +195,7 @@
     <t xml:space="preserve">Expediente CB-014 / Beneficiario Controlador</t>
   </si>
   <si>
-    <t xml:space="preserve">La columna K se calcula sola. Si dice SIN CERRAR, no está terminado: el nivel 3 cierra siempre, así que una casilla vacía ahí no significa que no haya Beneficiario Controlador, significa que falta buscarlo. · Los apoderados y mandatarios NO son Beneficiario Controlador por el hecho de serlo, y sus poderdantes tampoco lo son por el hecho de que ellos firmen: RCG 3 fr. IV, párrafo final. El poder acredita quién puede firmar, no quién manda.</t>
+    <t xml:space="preserve">La columna K se calcula sola. Si dice SIN CERRAR, no está terminado: el nivel 3 cierra siempre, así que una casilla vacía ahí no significa que no haya Beneficiario Controlador, significa que falta buscarlo. · Los apoderados y mandatarios NO son Beneficiario Controlador por el hecho de serlo, y sus poderdantes tampoco lo son por el hecho de que ellos firmen: RCG 3 fr. IV, párrafo final. El poder acredita quién puede firmar, no quién manda. · PERSONA MORAL SIN CAPITAL SOCIAL (asociación civil, sociedad civil sin partes sociales, cooperativa, asociación religiosa): el Nivel 1 no aplica porque no hay composición accionaria. Escriba «No aplica: la persona moral no tiene capital social representado en acciones o partes sociales» en la columna F y pase al Nivel 2 con estatutos y actas. No deje el campo en blanco. · SI EL CLIENTE SE NIEGA a dar la información, no se documenta el intento y se sigue: hay que ABSTENERSE de llevar a cabo el acto, y el artículo 21, segundo párrafo de la Ley dice que es SIN RESPONSABILIDAD ALGUNA. Cooperar y no alcanzar no es negarse; ahí se sigue la prelación hasta el tercer nivel.</t>
   </si>
   <si>
     <t xml:space="preserve">Cadena de control · el ascenso hasta la persona física</t>
@@ -273,7 +279,7 @@
     <t xml:space="preserve">2025-11-14</t>
   </si>
   <si>
-    <t xml:space="preserve">En el ejemplo, la cadena se detuvo cuando toda rama terminó en persona física. Jorge Peña Rivas controla el 85 % de una sociedad que tiene el 60 % del cliente: llega al Nivel 1 de la prelación por vía indirecta, que es exactamente lo que el RCG 23 Quinquies fr. I quiere decir con «directa o indirectamente». · Para fideicomisos, los candidatos que enlista el RCG 23 Quinquies 1 son fiduciario, fideicomitente, fideicomisario, la persona protectora y los miembros del comité técnico u órgano equivalente. La protectora es la que casi nunca aparece en los formatos del mercado.</t>
+    <t xml:space="preserve">EN LA CADENA NO SE MULTIPLICAN LOS PORCENTAJES. En el ejemplo, Jorge Peña Rivas tiene el 85 % de una sociedad que tiene el 60 % del cliente: el producto sería 51 %, y ese número no significa nada. Lo que se mide en cada eslabón es la capacidad de decidir, y él decide en la intermedia y la intermedia decide en el cliente. Es criterio del taller, no artículo: el texto sólo dice «directa o indirectamente». Quien multiplica porcentajes deja fuera a quien manda. · En el ejemplo, la cadena se detuvo cuando toda rama terminó en persona física. Jorge Peña Rivas controla el 85 % de una sociedad que tiene el 60 % del cliente: llega al Nivel 1 de la prelación por vía indirecta, que es exactamente lo que el RCG 23 Quinquies fr. I quiere decir con «directa o indirectamente». · Para fideicomisos, los candidatos que enlista el RCG 23 Quinquies 1 son fiduciario, fideicomitente, fideicomisario, la persona protectora y los miembros del comité técnico u órgano equivalente. La protectora es la que casi nunca aparece en los formatos del mercado.</t>
   </si>
   <si>
     <t xml:space="preserve">Las dos excepciones del RCG 23 Quinquies 2, y hasta dónde llegan</t>
@@ -1111,7 +1117,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:J29"/>
+  <dimension ref="A1:J32"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="1" style="0" width="22"/>
@@ -1470,7 +1476,7 @@
       <c r="I26" s="3"/>
       <c r="J26" s="3"/>
     </row>
-    <row r="27" customFormat="false" ht="23.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="27" customFormat="false" ht="57.45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="3" t="s">
         <v>25</v>
       </c>
@@ -1484,10 +1490,8 @@
       <c r="I27" s="3"/>
       <c r="J27" s="3"/>
     </row>
-    <row r="28" customFormat="false" ht="23.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A28" s="3" t="s">
-        <v>26</v>
-      </c>
+    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A28" s="3"/>
       <c r="B28" s="3"/>
       <c r="C28" s="3"/>
       <c r="D28" s="3"/>
@@ -1498,9 +1502,9 @@
       <c r="I28" s="3"/>
       <c r="J28" s="3"/>
     </row>
-    <row r="29" customFormat="false" ht="23.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="3" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B29" s="3"/>
       <c r="C29" s="3"/>
@@ -1512,8 +1516,50 @@
       <c r="I29" s="3"/>
       <c r="J29" s="3"/>
     </row>
+    <row r="30" customFormat="false" ht="23.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A30" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="B30" s="3"/>
+      <c r="C30" s="3"/>
+      <c r="D30" s="3"/>
+      <c r="E30" s="3"/>
+      <c r="F30" s="3"/>
+      <c r="G30" s="3"/>
+      <c r="H30" s="3"/>
+      <c r="I30" s="3"/>
+      <c r="J30" s="3"/>
+    </row>
+    <row r="31" customFormat="false" ht="23.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A31" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="B31" s="3"/>
+      <c r="C31" s="3"/>
+      <c r="D31" s="3"/>
+      <c r="E31" s="3"/>
+      <c r="F31" s="3"/>
+      <c r="G31" s="3"/>
+      <c r="H31" s="3"/>
+      <c r="I31" s="3"/>
+      <c r="J31" s="3"/>
+    </row>
+    <row r="32" customFormat="false" ht="23.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A32" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="B32" s="3"/>
+      <c r="C32" s="3"/>
+      <c r="D32" s="3"/>
+      <c r="E32" s="3"/>
+      <c r="F32" s="3"/>
+      <c r="G32" s="3"/>
+      <c r="H32" s="3"/>
+      <c r="I32" s="3"/>
+      <c r="J32" s="3"/>
+    </row>
   </sheetData>
-  <mergeCells count="54">
+  <mergeCells count="60">
     <mergeCell ref="A1:J1"/>
     <mergeCell ref="A2:J2"/>
     <mergeCell ref="A4:E4"/>
@@ -1568,6 +1614,12 @@
     <mergeCell ref="F28:J28"/>
     <mergeCell ref="A29:E29"/>
     <mergeCell ref="F29:J29"/>
+    <mergeCell ref="A30:E30"/>
+    <mergeCell ref="F30:J30"/>
+    <mergeCell ref="A31:E31"/>
+    <mergeCell ref="F31:J31"/>
+    <mergeCell ref="A32:E32"/>
+    <mergeCell ref="F32:J32"/>
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
@@ -1603,7 +1655,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -1621,7 +1673,7 @@
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
@@ -1639,71 +1691,71 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="6" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="7" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C6" s="7" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="D6" s="7" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="E6" s="7" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="F6" s="7" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="G6" s="7" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="H6" s="7" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="I6" s="7" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="J6" s="7" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="K6" s="7" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="L6" s="7" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="M6" s="7" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="N6" s="7" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="8" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="B7" s="8" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="C7" s="8" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="D7" s="8" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="E7" s="8" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="F7" s="8" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="G7" s="8"/>
       <c r="H7" s="8"/>
@@ -1714,13 +1766,13 @@
         <v>Nivel 1</v>
       </c>
       <c r="L7" s="8" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="M7" s="9" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="N7" s="8" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2350,9 +2402,9 @@
       <c r="M40" s="12"/>
       <c r="N40" s="10"/>
     </row>
-    <row r="42" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="42" customFormat="false" ht="32.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A42" s="13" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="B42" s="13"/>
       <c r="C42" s="13"/>
@@ -2411,7 +2463,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -2424,7 +2476,7 @@
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
@@ -2437,152 +2489,152 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="6" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="7" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="C6" s="7" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="D6" s="7" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="E6" s="7" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="F6" s="7" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="G6" s="7" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="H6" s="7" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="I6" s="7" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="8" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="B7" s="8" t="n">
         <v>1</v>
       </c>
       <c r="C7" s="8" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="D7" s="8" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="E7" s="8" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="F7" s="8" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="G7" s="8" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="H7" s="8" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="I7" s="9" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="8" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="B8" s="8" t="n">
         <v>2</v>
       </c>
       <c r="C8" s="8" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="D8" s="8" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="E8" s="8" t="s">
+        <v>73</v>
+      </c>
+      <c r="F8" s="8" t="s">
+        <v>50</v>
+      </c>
+      <c r="G8" s="8" t="s">
+        <v>74</v>
+      </c>
+      <c r="H8" s="8" t="s">
+        <v>75</v>
+      </c>
+      <c r="I8" s="9" t="s">
         <v>71</v>
-      </c>
-      <c r="F8" s="8" t="s">
-        <v>48</v>
-      </c>
-      <c r="G8" s="8" t="s">
-        <v>72</v>
-      </c>
-      <c r="H8" s="8" t="s">
-        <v>73</v>
-      </c>
-      <c r="I8" s="9" t="s">
-        <v>69</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="8" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="B9" s="8" t="n">
         <v>2</v>
       </c>
       <c r="C9" s="8" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="D9" s="8" t="s">
+        <v>77</v>
+      </c>
+      <c r="E9" s="8" t="s">
+        <v>78</v>
+      </c>
+      <c r="F9" s="8" t="s">
+        <v>51</v>
+      </c>
+      <c r="G9" s="8" t="s">
+        <v>79</v>
+      </c>
+      <c r="H9" s="8" t="s">
         <v>75</v>
       </c>
-      <c r="E9" s="8" t="s">
-        <v>76</v>
-      </c>
-      <c r="F9" s="8" t="s">
-        <v>49</v>
-      </c>
-      <c r="G9" s="8" t="s">
-        <v>77</v>
-      </c>
-      <c r="H9" s="8" t="s">
-        <v>73</v>
-      </c>
       <c r="I9" s="9" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="8" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="B10" s="8" t="n">
         <v>3</v>
       </c>
       <c r="C10" s="8" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="D10" s="8" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="E10" s="8" t="s">
+        <v>81</v>
+      </c>
+      <c r="F10" s="8" t="s">
+        <v>51</v>
+      </c>
+      <c r="G10" s="8" t="s">
         <v>79</v>
       </c>
-      <c r="F10" s="8" t="s">
-        <v>49</v>
-      </c>
-      <c r="G10" s="8" t="s">
-        <v>77</v>
-      </c>
       <c r="H10" s="8" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="I10" s="9" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2959,9 +3011,9 @@
       <c r="H44" s="10"/>
       <c r="I44" s="12"/>
     </row>
-    <row r="46" customFormat="false" ht="32.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="46" customFormat="false" ht="43.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A46" s="13" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="B46" s="13"/>
       <c r="C46" s="13"/>
@@ -3011,7 +3063,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -3021,7 +3073,7 @@
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
@@ -3031,67 +3083,67 @@
     </row>
     <row r="5" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="7" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="C5" s="7" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="D5" s="7" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="E5" s="7" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="F5" s="7" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="150" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="3" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="150" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="3" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="22.35" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="13" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="B9" s="13"/>
       <c r="C9" s="13"/>
@@ -3134,7 +3186,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -3145,7 +3197,7 @@
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
@@ -3156,189 +3208,189 @@
     </row>
     <row r="5" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="7" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="C5" s="7" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="D5" s="7" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="E5" s="7" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="F5" s="7" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="G5" s="7" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="3" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="G6" s="3"/>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="3" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="B7" s="3" t="s">
+        <v>122</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="E7" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="F7" s="3" t="s">
         <v>120</v>
-      </c>
-      <c r="C7" s="3" t="s">
-        <v>121</v>
-      </c>
-      <c r="D7" s="3" t="s">
-        <v>122</v>
-      </c>
-      <c r="E7" s="3" t="s">
-        <v>123</v>
-      </c>
-      <c r="F7" s="3" t="s">
-        <v>118</v>
       </c>
       <c r="G7" s="3"/>
     </row>
     <row r="8" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="3" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="3" t="s">
+        <v>132</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>133</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="D9" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="E9" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="F9" s="3" t="s">
         <v>130</v>
-      </c>
-      <c r="B9" s="3" t="s">
-        <v>131</v>
-      </c>
-      <c r="C9" s="3" t="s">
-        <v>125</v>
-      </c>
-      <c r="D9" s="3" t="s">
-        <v>132</v>
-      </c>
-      <c r="E9" s="3" t="s">
-        <v>133</v>
-      </c>
-      <c r="F9" s="3" t="s">
-        <v>128</v>
       </c>
       <c r="G9" s="3"/>
     </row>
     <row r="10" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="3" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="G10" s="3"/>
     </row>
     <row r="11" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="3" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="G11" s="3"/>
     </row>
     <row r="12" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="3" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="14" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="7" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="B16" s="7" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="C16" s="7"/>
       <c r="D16" s="7"/>
@@ -3348,10 +3400,10 @@
     </row>
     <row r="17" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="3" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="C17" s="3"/>
       <c r="D17" s="3"/>
@@ -3361,10 +3413,10 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="3" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="C18" s="3"/>
       <c r="D18" s="3"/>
@@ -3374,10 +3426,10 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="3" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="C19" s="3"/>
       <c r="D19" s="3"/>
@@ -3387,10 +3439,10 @@
     </row>
     <row r="20" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="3" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="C20" s="3"/>
       <c r="D20" s="3"/>
@@ -3400,7 +3452,7 @@
     </row>
     <row r="22" customFormat="false" ht="22.35" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="13" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="B22" s="13"/>
       <c r="C22" s="13"/>
@@ -3440,186 +3492,186 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
     </row>
     <row r="5" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="7" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="C5" s="7" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="3" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="3" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="3" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="3" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="3" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="3" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="3" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="B12" s="3" t="s">
+        <v>186</v>
+      </c>
+      <c r="C12" s="3" t="s">
         <v>184</v>
-      </c>
-      <c r="C12" s="3" t="s">
-        <v>182</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="3" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="3" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="3" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="3" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="B16" s="3" t="s">
+        <v>196</v>
+      </c>
+      <c r="C16" s="3" t="s">
         <v>194</v>
-      </c>
-      <c r="C16" s="3" t="s">
-        <v>192</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="3" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="3" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="3" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="22.35" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="13" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="B21" s="13"/>
       <c r="C21" s="13"/>

--- a/s04/descargables/S04_ALU_04_Checklist_Beneficiario_Controlador.xlsx
+++ b/s04/descargables/S04_ALU_04_Checklist_Beneficiario_Controlador.xlsx
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="236" uniqueCount="204">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="257" uniqueCount="218">
   <si>
     <t xml:space="preserve">Checklist de Beneficiario Controlador</t>
   </si>
@@ -279,7 +279,7 @@
     <t xml:space="preserve">2025-11-14</t>
   </si>
   <si>
-    <t xml:space="preserve">EN LA CADENA NO SE MULTIPLICAN LOS PORCENTAJES. En el ejemplo, Jorge Peña Rivas tiene el 85 % de una sociedad que tiene el 60 % del cliente: el producto sería 51 %, y ese número no significa nada. Lo que se mide en cada eslabón es la capacidad de decidir, y él decide en la intermedia y la intermedia decide en el cliente. Es criterio del taller, no artículo: el texto sólo dice «directa o indirectamente». Quien multiplica porcentajes deja fuera a quien manda. · En el ejemplo, la cadena se detuvo cuando toda rama terminó en persona física. Jorge Peña Rivas controla el 85 % de una sociedad que tiene el 60 % del cliente: llega al Nivel 1 de la prelación por vía indirecta, que es exactamente lo que el RCG 23 Quinquies fr. I quiere decir con «directa o indirectamente». · Para fideicomisos, los candidatos que enlista el RCG 23 Quinquies 1 son fiduciario, fideicomitente, fideicomisario, la persona protectora y los miembros del comité técnico u órgano equivalente. La protectora es la que casi nunca aparece en los formatos del mercado.</t>
+    <t xml:space="preserve">EN LA CADENA NO SE MULTIPLICAN LOS PORCENTAJES. En el ejemplo, Jorge Peña Rivas tiene el 85 % de una sociedad que tiene el 60 % del cliente: el producto sería 51 %, y ese número no significa nada. Lo que se mide en cada eslabón es la capacidad de decidir, y él decide en la intermedia y la intermedia decide en el cliente. Es criterio del taller, no artículo: el texto sólo dice «directa o indirectamente». Quien multiplica porcentajes deja fuera a quien manda. · En el ejemplo, la cadena se detuvo cuando toda rama terminó en persona física. Jorge Peña Rivas controla el 85 % de una sociedad que tiene el 60 % del cliente: llega al Nivel 1 de la prelación por vía indirecta, que es exactamente lo que el RCG 23 Quinquies fr. I quiere decir con «directa o indirectamente». · Para fideicomisos, los candidatos que enlista el RCG 23 Quinquies 1 son fiduciario, fideicomitente, fideicomisario, la persona protectora y los miembros del comité técnico u órgano equivalente. La protectora es la que casi nunca aparece en los formatos del mercado. · DÓNDE SE LEE EL CONTROL EN UN FIDEICOMISO. La LFPIORPI no define qué es un fideicomitente ni qué facultades tiene: eso está en la LGTOC, supletoria por el L 4 fr. II Bis, fracción adicionada el 16 de julio de 2025. La LGTOC dice qué es cada figura y qué puede hacer, y con eso se resuelve el test de control; no funda ninguna obligación de este régimen. Tres pruebas, las tres se leen en el acto constitutivo: (1) LGTOC 386 segundo párrafo, si el fideicomitente se reservó expresamente derechos y acciones sobre los bienes, no salió de la operación; (2) LGTOC 392 fr. VI, si se reservó el derecho de revocar, puede extinguir el fideicomiso, y quien puede extinguirlo manda; (3) LGTOC 382 tercer párrafo, el fideicomiso es válido aunque se constituya sin fideicomisario designado, de modo que su ausencia no detiene la identificación: el control se busca en las demás figuras y se asienta por qué no había fideicomisario. · Con dos o más fideicomisarios, el LGTOC 383 computa los votos POR REPRESENTACIONES Y NO POR PERSONAS: no se cuenta por cabeza. · El delegado fiduciario, que es quien realmente ejerce las facultades del fiduciario, está en el LIC 80 y NO aparece en el catálogo del RCG 23 Quinquies 1. Por la definición funcional es candidato natural; por la letra, no está en la lista. Documentarlo deja mejor parado que omitirlo, pero no se presente como obligación. · Ante un cliente que se niega a informar quiénes intervienen: los fideicomisos secretos están prohibidos por el LGTOC 394 fr. I desde 1932.</t>
   </si>
   <si>
     <t xml:space="preserve">Las dos excepciones del RCG 23 Quinquies 2, y hasta dónde llegan</t>
@@ -634,6 +634,48 @@
   </si>
   <si>
     <t xml:space="preserve">El Capítulo III Quinquies aplica a los actos u operaciones desde el 1 de marzo de 2027.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">L 4 fr. II Bis</t>
+  </si>
+  <si>
+    <t xml:space="preserve">La Ley General de Títulos y Operaciones de Crédito es supletoria de la LFPIORPI. Fracción ADICIONADA por el DOF del 16 de julio de 2025.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LGTOC 386, segundo párrafo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Los bienes quedan afectos al fin, «salvo los que expresamente se reserve el fideicomitente». La reserva expresa de derechos es indicador de control.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LGTOC 392 fr. VI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">El fideicomiso se extingue por revocación del fideicomitente «cuando éste se haya reservado expresamente ese derecho al constituir el fideicomiso». Quien puede extinguirlo, manda.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LGTOC 382, tercer párrafo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">El fideicomiso es válido aunque se constituya sin señalar fideicomisario, si el fin es lícito y determinado y consta la aceptación del encargo por el fiduciario.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LGTOC 383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Con dos o más fideicomisarios, las decisiones se toman por mayoría de votos computados POR REPRESENTACIONES Y NO POR PERSONAS.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LGTOC 394 fr. I</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Los fideicomisos secretos están prohibidos. Vigente desde 1932.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LIC 80</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Crea al comité técnico y al delegado fiduciario. El delegado fiduciario NO aparece en el catálogo del RCG 23 Quinquies 1.</t>
   </si>
   <si>
     <t xml:space="preserve">El dato histórico del umbral está cotejado: el texto original de la Ley publicado el 17 de octubre de 2012 decía «más del cincuenta por ciento del capital social» en el subinciso ii), y ese subinciso fue reformado por el DOF del 16 de julio de 2025 para quedar en «más del veinticinco por ciento».</t>
@@ -3011,7 +3053,7 @@
       <c r="H44" s="10"/>
       <c r="I44" s="12"/>
     </row>
-    <row r="46" customFormat="false" ht="43.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="46" customFormat="false" ht="105.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A46" s="13" t="s">
         <v>84</v>
       </c>
@@ -3482,7 +3524,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:C21"/>
+  <dimension ref="A1:C28"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="32"/>
@@ -3669,18 +3711,95 @@
         <v>171</v>
       </c>
     </row>
-    <row r="21" customFormat="false" ht="22.35" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A21" s="13" t="s">
+    <row r="20" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="3" t="s">
         <v>203</v>
       </c>
-      <c r="B21" s="13"/>
-      <c r="C21" s="13"/>
+      <c r="B20" s="3" t="s">
+        <v>204</v>
+      </c>
+      <c r="C20" s="3" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A21" s="3" t="s">
+        <v>205</v>
+      </c>
+      <c r="B21" s="3" t="s">
+        <v>206</v>
+      </c>
+      <c r="C21" s="3" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A22" s="3" t="s">
+        <v>207</v>
+      </c>
+      <c r="B22" s="3" t="s">
+        <v>208</v>
+      </c>
+      <c r="C22" s="3" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A23" s="3" t="s">
+        <v>209</v>
+      </c>
+      <c r="B23" s="3" t="s">
+        <v>210</v>
+      </c>
+      <c r="C23" s="3" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A24" s="3" t="s">
+        <v>211</v>
+      </c>
+      <c r="B24" s="3" t="s">
+        <v>212</v>
+      </c>
+      <c r="C24" s="3" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A25" s="3" t="s">
+        <v>213</v>
+      </c>
+      <c r="B25" s="3" t="s">
+        <v>214</v>
+      </c>
+      <c r="C25" s="3" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A26" s="3" t="s">
+        <v>215</v>
+      </c>
+      <c r="B26" s="3" t="s">
+        <v>216</v>
+      </c>
+      <c r="C26" s="3" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="28" customFormat="false" ht="22.35" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A28" s="13" t="s">
+        <v>217</v>
+      </c>
+      <c r="B28" s="13"/>
+      <c r="C28" s="13"/>
     </row>
   </sheetData>
   <mergeCells count="3">
     <mergeCell ref="A1:C1"/>
     <mergeCell ref="A2:C2"/>
-    <mergeCell ref="A21:C21"/>
+    <mergeCell ref="A28:C28"/>
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
